--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484683_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484683_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7048</v>
+        <v>6.7976</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4699</v>
+        <v>6.9095</v>
       </c>
       <c r="F2" t="n">
-        <v>0.235</v>
+        <v>-0.1119</v>
       </c>
       <c r="G2" t="n">
         <v>5.0289</v>
@@ -610,13 +610,13 @@
         <v>2.3823</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3949</v>
+        <v>-0.302</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5694</v>
+        <v>-0.1297</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1745</v>
+        <v>-0.1723</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3115</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2965</v>
+        <v>1.467</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5756</v>
+        <v>1.6717</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2791</v>
+        <v>-0.2047</v>
       </c>
       <c r="G3" t="n">
         <v>1.1082</v>
@@ -688,13 +688,13 @@
         <v>1.2828</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8117</v>
+        <v>-0.6412</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4955</v>
+        <v>-0.3993</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3162</v>
+        <v>-0.2419</v>
       </c>
       <c r="V3" t="n">
         <v>0.6335</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. TORCOLETTI</t>
+          <t>M. BALFAGON SULLER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3093</v>
+        <v>-0.2261</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0457</v>
+        <v>-0.2788</v>
       </c>
       <c r="F5" t="n">
-        <v>0.355</v>
+        <v>0.0527</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0745</v>
+        <v>-0.881</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1068</v>
+        <v>0.0037</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0323</v>
+        <v>-0.8847</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3919</v>
+        <v>0.1617</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1143</v>
+        <v>0.0525</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5062</v>
+        <v>0.1091</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3173</v>
+        <v>-1.0427</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2211</v>
+        <v>-0.0489</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5385</v>
+        <v>-0.9938</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0995</v>
+        <v>0.733</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0158</v>
+        <v>0.733</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5616</v>
+        <v>-0.7012</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2625</v>
+        <v>-0.4404</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7008</v>
+        <v>-0.2608</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2774</v>
+        <v>0.6231</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2774</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. BALFAGON SULLER</t>
+          <t>F. TORCOLETTI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3004</v>
+        <v>-0.4267</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2788</v>
+        <v>-0.856</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0217</v>
+        <v>0.4293</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.881</v>
+        <v>-0.0745</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0037</v>
+        <v>-1.1068</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8847</v>
+        <v>1.0323</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1617</v>
+        <v>-0.3919</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0525</v>
+        <v>0.1143</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1091</v>
+        <v>-0.5062</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0427</v>
+        <v>0.3173</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0489</v>
+        <v>-1.2211</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9938</v>
+        <v>1.5385</v>
       </c>
       <c r="P6" t="n">
-        <v>0.733</v>
+        <v>1.0995</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>0.733</v>
+        <v>2.0158</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7755</v>
+        <v>-0.1744</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4404</v>
+        <v>0.4521</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3351</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6231</v>
+        <v>-1.2774</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6231</v>
+        <v>-1.2774</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6431</v>
+        <v>-0.7174</v>
       </c>
       <c r="E7" t="n">
         <v>-1.7626</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1195</v>
+        <v>1.0452</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5573</v>
@@ -1000,13 +1000,13 @@
         <v>0.9163</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0858</v>
+        <v>-0.1601</v>
       </c>
       <c r="T7" t="n">
         <v>-0.3303</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2446</v>
+        <v>0.1702</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8639</v>
+        <v>-0.8581</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1576</v>
+        <v>-0.0347</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0216</v>
+        <v>-0.8234</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3513</v>
@@ -1078,13 +1078,13 @@
         <v>0.9163</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.162</v>
+        <v>-0.1561</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0905</v>
+        <v>-0.1018</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2525</v>
+        <v>-0.0543</v>
       </c>
       <c r="V8" t="n">
         <v>-1.267</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9011</v>
+        <v>-2.1152</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4657</v>
+        <v>0.1772</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3668</v>
+        <v>-2.2924</v>
       </c>
       <c r="G9" t="n">
         <v>-3.5102</v>
@@ -1156,13 +1156,13 @@
         <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0244</v>
+        <v>-0.2385</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3107</v>
+        <v>0.0223</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3351</v>
+        <v>-0.2608</v>
       </c>
       <c r="V9" t="n">
         <v>1.267</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2722</v>
+        <v>-2.1865</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0772</v>
+        <v>-0.2145</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.195</v>
+        <v>-1.972</v>
       </c>
       <c r="G10" t="n">
         <v>-0.06859999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>2.3823</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5934</v>
+        <v>-1.5077</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2586</v>
+        <v>-0.3959</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3348</v>
+        <v>-1.1118</v>
       </c>
       <c r="V10" t="n">
         <v>1.5889</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9798</v>
+        <v>-2.6884</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4279</v>
+        <v>-0.2356</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5518</v>
+        <v>-2.4527</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5483</v>
@@ -1312,13 +1312,13 @@
         <v>1.2828</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8321</v>
+        <v>-0.5407</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4593</v>
+        <v>-0.267</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3729</v>
+        <v>-0.2738</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9658</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>M. CALANCHE GONZALEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9395</v>
+        <v>-4.3452</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1663</v>
+        <v>-2.3374</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7732</v>
+        <v>-2.0078</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.4928</v>
+        <v>-1.7539</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.5019</v>
+        <v>0.1084</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9909</v>
+        <v>-1.8623</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3253</v>
+        <v>-0.38</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.617</v>
+        <v>1.418</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2917</v>
+        <v>-1.7981</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.1676</v>
+        <v>-1.3739</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.8849</v>
+        <v>-1.3097</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2827</v>
+        <v>-0.0643</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7489</v>
+        <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5875</v>
+        <v>-0.2247</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.058</v>
+        <v>-0.1248</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6455</v>
+        <v>-0.0999</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9658</v>
+        <v>-1.267</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9658</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. CALANCHE GONZALEZ</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1287</v>
+        <v>-4.82</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8732</v>
+        <v>-3.3036</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2555</v>
+        <v>-1.5164</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7539</v>
+        <v>-5.4928</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1084</v>
+        <v>-4.5019</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8623</v>
+        <v>-0.9909</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.38</v>
+        <v>-1.3253</v>
       </c>
       <c r="K13" t="n">
-        <v>1.418</v>
+        <v>-1.617</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.7981</v>
+        <v>0.2917</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3739</v>
+        <v>-4.1676</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3097</v>
+        <v>-2.8849</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0643</v>
+        <v>-1.2827</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.0995</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R13" t="n">
-        <v>0.733</v>
+        <v>2.7489</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0083</v>
+        <v>-0.293</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6606</v>
+        <v>-0.1953</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3477</v>
+        <v>-0.0977</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.267</v>
+        <v>0.9658</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.9658</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.281599999999999</v>
+        <v>-7.6056</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.878</v>
+        <v>-3.3011</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.4036</v>
+        <v>-4.3046</v>
       </c>
       <c r="G14" t="n">
         <v>-7.2451</v>
@@ -1546,13 +1546,13 @@
         <v>1.6493</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4188</v>
+        <v>-0.7428</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7896</v>
+        <v>-0.2126</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6293</v>
+        <v>-0.5302</v>
       </c>
       <c r="V14" t="n">
         <v>-1.267</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-17.3746</v>
+        <v>-17.0995</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.215800000000001</v>
+        <v>-2.940799999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-14.1588</v>
+        <v>-14.1587</v>
       </c>
       <c r="G15" t="n">
         <v>-14.7208</v>
@@ -1624,10 +1624,10 @@
         <v>17.4093</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.9578</v>
+        <v>-5.6824</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.398</v>
+        <v>-2.1227</v>
       </c>
       <c r="U15" t="n">
         <v>-3.5598</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MONRABAL ROMEU</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.0984</v>
+        <v>7.0109</v>
       </c>
       <c r="E16" t="n">
-        <v>6.7475</v>
+        <v>6.5713</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3509</v>
+        <v>0.4396</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7063</v>
+        <v>3.1746</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3981</v>
+        <v>2.6872</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3082</v>
+        <v>0.4874</v>
       </c>
       <c r="J16" t="n">
-        <v>7.6667</v>
+        <v>3.8284</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9477</v>
+        <v>2.8919</v>
       </c>
       <c r="L16" t="n">
-        <v>4.719</v>
+        <v>0.9365</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9605</v>
+        <v>-0.6538</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5496</v>
+        <v>-0.2047</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4109</v>
+        <v>-0.4492</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.0995</v>
+        <v>1.4661</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9321</v>
+        <v>-0.1833</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8326</v>
+        <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4917</v>
+        <v>1.1137</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0128</v>
+        <v>0.3922</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4789</v>
+        <v>0.7215</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.2566</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2774</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>A. MONRABAL ROMEU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.4383</v>
+        <v>6.201</v>
       </c>
       <c r="E17" t="n">
-        <v>6.379</v>
+        <v>5.5936</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0593</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1746</v>
+        <v>5.7063</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6872</v>
+        <v>2.3981</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4874</v>
+        <v>3.3082</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8284</v>
+        <v>7.6667</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8919</v>
+        <v>2.9477</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9365</v>
+        <v>4.719</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6538</v>
+        <v>-1.9605</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2047</v>
+        <v>-0.5496</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4492</v>
+        <v>-1.4109</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4661</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1833</v>
+        <v>-2.9321</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6493</v>
+        <v>1.8326</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5411</v>
+        <v>1.5943</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1999</v>
+        <v>0.859</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3412</v>
+        <v>0.7353</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2566</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.9479</v>
+        <v>3.7233</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7954</v>
+        <v>2.6212</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1525</v>
+        <v>1.1021</v>
       </c>
       <c r="G18" t="n">
-        <v>4.923</v>
+        <v>1.0862</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8011</v>
+        <v>2.2754</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1219</v>
+        <v>-1.1892</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9403</v>
+        <v>1.2728</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5234</v>
+        <v>1.8206</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4169</v>
+        <v>-0.5478</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9827</v>
+        <v>-0.1866</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2777</v>
+        <v>0.4548</v>
       </c>
       <c r="O18" t="n">
-        <v>0.705</v>
+        <v>-0.6413</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1833</v>
+        <v>1.0995</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>1.0995</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2683</v>
+        <v>0.2705</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6056</v>
+        <v>0.0815</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3373</v>
+        <v>0.1891</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.89</v>
+        <v>1.267</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6231</v>
+        <v>1.267</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.9234</v>
+        <v>3.4506</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0443</v>
+        <v>2.3723</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8791</v>
+        <v>1.0782</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0862</v>
+        <v>4.923</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2754</v>
+        <v>2.8011</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1892</v>
+        <v>2.1219</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2728</v>
+        <v>3.9403</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8206</v>
+        <v>2.5234</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5478</v>
+        <v>1.4169</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1866</v>
+        <v>0.9827</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4548</v>
+        <v>0.2777</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6413</v>
+        <v>0.705</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0995</v>
+        <v>0.1833</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R19" t="n">
         <v>1.0995</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5293</v>
+        <v>0.2343</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4955</v>
+        <v>-0.0286</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0339</v>
+        <v>0.263</v>
       </c>
       <c r="V19" t="n">
-        <v>1.267</v>
+        <v>-1.89</v>
       </c>
       <c r="W19" t="n">
-        <v>1.267</v>
+        <v>-0.6231</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.7436</v>
+        <v>3.2259</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6473</v>
+        <v>2.5511</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0963</v>
+        <v>0.6748</v>
       </c>
       <c r="G20" t="n">
         <v>2.0298</v>
@@ -2014,13 +2014,13 @@
         <v>0.733</v>
       </c>
       <c r="S20" t="n">
-        <v>1.002</v>
+        <v>1.4843</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2263</v>
+        <v>1.1301</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2242</v>
+        <v>0.3542</v>
       </c>
       <c r="V20" t="n">
         <v>1.9109</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.9393</v>
+        <v>1.9068</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8577</v>
+        <v>2.1509</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0816</v>
+        <v>-0.244</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7357</v>
+        <v>1.0904</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9187</v>
+        <v>2.0683</v>
       </c>
       <c r="I21" t="n">
-        <v>-5.6544</v>
+        <v>-0.9779</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.2055</v>
+        <v>3.3285</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5573</v>
+        <v>1.8699</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.7628</v>
+        <v>1.4586</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5302</v>
+        <v>-2.2382</v>
       </c>
       <c r="N21" t="n">
-        <v>1.3614</v>
+        <v>0.1983</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8916</v>
+        <v>-2.4365</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1991</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1991</v>
+        <v>1.4661</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2089</v>
+        <v>1.0443</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1524</v>
+        <v>0.5162</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0565</v>
+        <v>0.5281</v>
       </c>
       <c r="V21" t="n">
-        <v>1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="W21" t="n">
-        <v>1.9109</v>
+        <v>0.3219</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.579</v>
+        <v>1.2662</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0547</v>
+        <v>0.1846</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4757</v>
+        <v>1.0816</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0904</v>
+        <v>-2.7357</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0683</v>
+        <v>2.9187</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9779</v>
+        <v>-5.6544</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3285</v>
+        <v>-2.2055</v>
       </c>
       <c r="K22" t="n">
-        <v>1.8699</v>
+        <v>1.5573</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4586</v>
+        <v>-3.7628</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2382</v>
+        <v>-0.5302</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1983</v>
+        <v>1.3614</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.4365</v>
+        <v>-1.8916</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5498</v>
+        <v>2.1991</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4661</v>
+        <v>2.1991</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7165</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4201</v>
+        <v>0.4793</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2964</v>
+        <v>0.0565</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3219</v>
+        <v>1.9109</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9534</v>
+        <v>-0.9973</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.984</v>
+        <v>-0.8879</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0306</v>
+        <v>-0.1094</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0933</v>
@@ -2248,13 +2248,13 @@
         <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1845</v>
+        <v>1.1406</v>
       </c>
       <c r="T23" t="n">
-        <v>0.31</v>
+        <v>0.4061</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.7345</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3115</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.0718</v>
+        <v>-1.0223</v>
       </c>
       <c r="E24" t="n">
         <v>-1.911</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.8888</v>
       </c>
       <c r="G24" t="n">
         <v>0.5995</v>
@@ -2326,13 +2326,13 @@
         <v>0.5498</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3885</v>
+        <v>-0.339</v>
       </c>
       <c r="T24" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2234</v>
+        <v>-0.1738</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9101</v>
+        <v>-2.6246</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5476</v>
+        <v>-3.163</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6375</v>
+        <v>0.5384</v>
       </c>
       <c r="G25" t="n">
         <v>0.1815</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1204</v>
+        <v>0.1652</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2753</v>
+        <v>0.1094</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1549</v>
+        <v>0.0558</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9554</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.3599</v>
+        <v>-3.4837</v>
       </c>
       <c r="E26" t="n">
         <v>-1.9244</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.4355</v>
+        <v>-1.5593</v>
       </c>
       <c r="G26" t="n">
         <v>-0.2412</v>
@@ -2482,13 +2482,13 @@
         <v>0.1833</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1195</v>
+        <v>-0.0043</v>
       </c>
       <c r="T26" t="n">
         <v>-0.2202</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3397</v>
+        <v>0.2159</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5889</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>17.3747</v>
+        <v>18.6568</v>
       </c>
       <c r="E27" t="n">
-        <v>14.1589</v>
+        <v>14.1587</v>
       </c>
       <c r="F27" t="n">
-        <v>3.2158</v>
+        <v>4.498200000000001</v>
       </c>
       <c r="G27" t="n">
         <v>14.7211</v>
@@ -2560,13 +2560,13 @@
         <v>12.828</v>
       </c>
       <c r="S27" t="n">
-        <v>5.957700000000001</v>
+        <v>7.2397</v>
       </c>
       <c r="T27" t="n">
-        <v>3.559700000000001</v>
+        <v>3.5598</v>
       </c>
       <c r="U27" t="n">
-        <v>2.3979</v>
+        <v>3.6801</v>
       </c>
       <c r="V27" t="n">
         <v>1.2776</v>
